--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\001_Academic\002_Course_Works\003_2026_Sping_Semester\003_Low-Carbon Technologies and Policies\000_ICP_BL\006_Cambodia_TIMES_Model_V002\KHM_TIMES_V002_20260606\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serey\Downloads\Cambodia-TIMES-Model-main\Cambodia-TIMES-Model-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97F2325-7975-44E5-B4A2-0F8F2385987B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B7F02A-CB2B-4781-A4F7-04D1C3FB88CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -32,6 +32,19 @@
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -8989,26 +9002,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA35"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="10.88671875" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="10.88671875" customWidth="1"/>
-    <col min="22" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
       <c r="X1" s="20" t="s">
         <v>92</v>
       </c>
@@ -9022,7 +9035,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D2" s="35" t="s">
         <v>44</v>
       </c>
@@ -9090,7 +9103,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="2:27" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:27" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C3" s="59" t="s">
         <v>125</v>
       </c>
@@ -9152,7 +9165,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B4" s="33"/>
       <c r="C4" s="76" t="s">
         <v>57</v>
@@ -9176,7 +9189,7 @@
       <c r="U4" s="5"/>
       <c r="V4" s="77"/>
     </row>
-    <row r="5" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="37" t="s">
         <v>58</v>
       </c>
@@ -9260,7 +9273,7 @@
         <v>53.616579479999999</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B6" s="37" t="s">
         <v>60</v>
       </c>
@@ -9344,7 +9357,7 @@
         <v>17.352778751999999</v>
       </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
         <v>62</v>
       </c>
@@ -9428,7 +9441,7 @@
         <v>105.16278636</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B8" s="37" t="s">
         <v>64</v>
       </c>
@@ -9512,7 +9525,7 @@
         <v>8.9932882680000006</v>
       </c>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B9" s="37" t="s">
         <v>66</v>
       </c>
@@ -9596,7 +9609,7 @@
         <v>101.39634108000001</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B10" s="37" t="s">
         <v>68</v>
       </c>
@@ -9680,7 +9693,7 @@
         <v>9.4588185599999992</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B11" s="37" t="s">
         <v>85</v>
       </c>
@@ -9764,7 +9777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B12" s="37" t="s">
         <v>86</v>
       </c>
@@ -9848,7 +9861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B13" s="75" t="s">
         <v>88</v>
       </c>
@@ -9932,7 +9945,7 @@
         <v>295.9805925</v>
       </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -9943,7 +9956,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -9954,7 +9967,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="C16" s="42" t="s">
         <v>147</v>
       </c>
@@ -9969,7 +9982,7 @@
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -9980,7 +9993,7 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -9991,7 +10004,7 @@
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
     </row>
-    <row r="19" spans="2:24" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B19" s="22" t="s">
         <v>100</v>
       </c>
@@ -10056,7 +10069,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B20" s="37" t="s">
         <v>64</v>
       </c>
@@ -10089,7 +10102,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="21" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="37" t="s">
         <v>64</v>
       </c>
@@ -10122,7 +10135,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B22" s="37" t="s">
         <v>64</v>
       </c>
@@ -10155,7 +10168,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B23" s="82" t="s">
         <v>58</v>
       </c>
@@ -10192,7 +10205,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="82" t="s">
         <v>58</v>
       </c>
@@ -10225,7 +10238,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B25" s="82" t="s">
         <v>58</v>
       </c>
@@ -10265,7 +10278,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B26" s="82" t="s">
         <v>60</v>
       </c>
@@ -10300,7 +10313,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B27" s="82" t="s">
         <v>60</v>
       </c>
@@ -10333,7 +10346,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B28" s="82" t="s">
         <v>60</v>
       </c>
@@ -10352,7 +10365,10 @@
       <c r="J28" s="96"/>
       <c r="K28" s="96"/>
       <c r="L28" s="96"/>
-      <c r="M28" s="96"/>
+      <c r="M28" s="100">
+        <f>1-M26-M27</f>
+        <v>1</v>
+      </c>
       <c r="N28" s="96"/>
       <c r="O28" s="96"/>
       <c r="P28" s="96"/>
@@ -10370,7 +10386,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C31" s="55" t="s">
         <v>107</v>
       </c>
@@ -10381,7 +10397,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
         <v>117</v>
       </c>
@@ -10395,7 +10411,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="37" t="s">
         <v>64</v>
       </c>
@@ -10405,7 +10421,7 @@
       <c r="D33" s="87"/>
       <c r="E33" s="88"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="37" t="s">
         <v>58</v>
       </c>
@@ -10415,7 +10431,7 @@
       <c r="D34" s="53"/>
       <c r="E34" s="90"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="37" t="s">
         <v>60</v>
       </c>
@@ -10434,20 +10450,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B3:R24"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" customWidth="1"/>
-    <col min="14" max="14" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="29" t="s">
         <v>155</v>
       </c>
@@ -10464,7 +10480,7 @@
       <c r="M3" s="29"/>
       <c r="N3" s="29"/>
     </row>
-    <row r="4" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>
@@ -10473,7 +10489,7 @@
       <c r="G4" s="30"/>
       <c r="H4" s="30"/>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B5" s="28" t="s">
         <v>142</v>
       </c>
@@ -10484,7 +10500,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
         <v>0</v>
       </c>
@@ -10541,7 +10557,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>90</v>
       </c>
@@ -10589,7 +10605,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B8" t="str">
         <f>DemTechs_AGR!$P8</f>
         <v>AGRCO2</v>
@@ -10640,13 +10656,13 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="39"/>
       <c r="C23" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="61"/>
       <c r="C24" s="1" t="s">
         <v>150</v>
@@ -10661,20 +10677,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:J5"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.88671875" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" customWidth="1"/>
+    <col min="1" max="1" width="1.85546875" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="67" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="E5" s="68" t="s">
         <v>158</v>
       </c>
@@ -10694,29 +10710,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R41"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -10737,7 +10753,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B8</f>
         <v>AGR</v>
@@ -10773,7 +10789,7 @@
       <c r="Q2" s="124"/>
       <c r="R2" s="124"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J3" s="125" t="s">
         <v>7</v>
       </c>
@@ -10802,7 +10818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -10836,7 +10852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="66"/>
@@ -10862,7 +10878,7 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="128"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="66"/>
@@ -10886,7 +10902,7 @@
       <c r="Q6" s="128"/>
       <c r="R6" s="128"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="66"/>
@@ -10910,7 +10926,7 @@
       <c r="Q7" s="128"/>
       <c r="R7" s="128"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="66"/>
@@ -10934,7 +10950,7 @@
       <c r="Q8" s="128"/>
       <c r="R8" s="128"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="66"/>
@@ -10962,18 +10978,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="66"/>
       <c r="H10" s="10"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
@@ -10991,7 +11007,7 @@
       <c r="Q12" s="128"/>
       <c r="R12" s="128"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
@@ -11041,7 +11057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:18" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
         <v>39</v>
       </c>
@@ -11091,7 +11107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>90</v>
       </c>
@@ -11118,7 +11134,7 @@
       <c r="Q15" s="130"/>
       <c r="R15" s="130"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
         <f>L16</f>
         <v>FTE-AGRCOA</v>
@@ -11162,7 +11178,7 @@
       <c r="Q16" s="128"/>
       <c r="R16" s="128"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-AGRGAS</v>
@@ -11204,7 +11220,7 @@
       <c r="Q17" s="128"/>
       <c r="R17" s="128"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-AGROIL</v>
@@ -11249,7 +11265,7 @@
       <c r="Q18" s="128"/>
       <c r="R18" s="128"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="str">
         <f>'EB1'!$H$2</f>
         <v>KER</v>
@@ -11282,7 +11298,7 @@
       <c r="Q19" s="128"/>
       <c r="R19" s="128"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
         <f>'EB1'!$I$2</f>
         <v>LPG</v>
@@ -11317,7 +11333,7 @@
       <c r="Q20" s="128"/>
       <c r="R20" s="128"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
         <f>'EB1'!$J$2</f>
         <v>GSL</v>
@@ -11330,7 +11346,7 @@
       <c r="H21" s="10"/>
       <c r="M21" s="19"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
         <f>'EB1'!$L$2</f>
         <v>HFO</v>
@@ -11343,7 +11359,7 @@
       <c r="H22" s="10"/>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
         <f>'EB1'!$M$2</f>
         <v>OPP</v>
@@ -11356,7 +11372,7 @@
       <c r="H23" s="10"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B24" t="str">
         <f>L19</f>
         <v>FTE-AGRBIO</v>
@@ -11380,7 +11396,7 @@
       <c r="K24" s="23"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-AGRELC</v>
@@ -11407,7 +11423,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="66"/>
@@ -11416,20 +11432,20 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="66"/>
       <c r="H27" s="10"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B29" s="23"/>
       <c r="D29" s="23"/>
       <c r="E29" s="11"/>
@@ -11437,7 +11453,7 @@
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="11"/>
@@ -11445,7 +11461,7 @@
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="95"/>
@@ -11453,7 +11469,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="95"/>
@@ -11461,7 +11477,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -11469,7 +11485,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -11477,7 +11493,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="11"/>
@@ -11485,7 +11501,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="11"/>
@@ -11493,13 +11509,13 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="39"/>
       <c r="C40" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="61"/>
       <c r="C41" s="1" t="s">
         <v>150</v>
@@ -11516,33 +11532,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:V31"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5546875" customWidth="1"/>
-    <col min="12" max="12" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" customWidth="1"/>
     <col min="13" max="13" width="2" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" customWidth="1"/>
-    <col min="16" max="16" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="77.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.6640625" customWidth="1"/>
-    <col min="19" max="19" width="11.6640625" customWidth="1"/>
-    <col min="20" max="20" width="13.44140625" customWidth="1"/>
-    <col min="21" max="21" width="13.88671875" customWidth="1"/>
-    <col min="22" max="22" width="8.44140625" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" customWidth="1"/>
+    <col min="16" max="16" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.7109375" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:22" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -11567,7 +11583,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="2:22" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:22" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B8</f>
         <v>AGR</v>
@@ -11608,7 +11624,7 @@
       <c r="U2" s="124"/>
       <c r="V2" s="124"/>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="N3" s="125" t="s">
         <v>7</v>
       </c>
@@ -11637,7 +11653,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:22" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:22" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -11672,7 +11688,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -11700,7 +11716,7 @@
       <c r="U5" s="124"/>
       <c r="V5" s="124"/>
     </row>
-    <row r="6" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -11728,7 +11744,7 @@
       <c r="U6" s="124"/>
       <c r="V6" s="124"/>
     </row>
-    <row r="7" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -11756,7 +11772,7 @@
       <c r="U7" s="124"/>
       <c r="V7" s="124"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="N8" s="128" t="s">
         <v>106</v>
       </c>
@@ -11778,7 +11794,7 @@
       <c r="U8" s="128"/>
       <c r="V8" s="128"/>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
@@ -11800,7 +11816,7 @@
       <c r="U10" s="128"/>
       <c r="V10" s="128"/>
     </row>
-    <row r="11" spans="2:22" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B11" s="17" t="s">
         <v>1</v>
       </c>
@@ -11860,7 +11876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:22" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:22" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
@@ -11918,7 +11934,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:22" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>90</v>
       </c>
@@ -11950,7 +11966,7 @@
       <c r="U13" s="127"/>
       <c r="V13" s="127"/>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
         <f>P14</f>
         <v>APUMPEDSL</v>
@@ -12006,7 +12022,7 @@
         <v>PJa</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B15" t="str">
         <f>P15</f>
         <v>AMANCEDSL</v>
@@ -12065,7 +12081,7 @@
       <c r="U15" s="128"/>
       <c r="V15" s="128"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
         <f>P16</f>
         <v>AOTHEDSL</v>
@@ -12120,56 +12136,56 @@
         <v>PJa</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
       <c r="Q17" s="19"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
       <c r="Q18" s="19"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
       <c r="F19" s="95"/>
       <c r="G19" s="95"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
       <c r="F20" s="110"/>
       <c r="G20" s="110"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B26" s="39"/>
       <c r="C26" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B27" s="61"/>
       <c r="C27" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
       <c r="M30" s="1"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
       <c r="M31" s="1"/>
     </row>
   </sheetData>
@@ -12184,29 +12200,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:R42"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -12227,7 +12243,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B6</f>
         <v>COM</v>
@@ -12263,7 +12279,7 @@
       <c r="Q2" s="124"/>
       <c r="R2" s="124"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J3" s="125" t="s">
         <v>7</v>
       </c>
@@ -12292,7 +12308,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -12326,7 +12342,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="66"/>
@@ -12352,7 +12368,7 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="128"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="66"/>
@@ -12376,7 +12392,7 @@
       <c r="Q6" s="128"/>
       <c r="R6" s="128"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="66"/>
@@ -12400,7 +12416,7 @@
       <c r="Q7" s="128"/>
       <c r="R7" s="128"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="66"/>
@@ -12424,7 +12440,7 @@
       <c r="Q8" s="128"/>
       <c r="R8" s="128"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="66"/>
@@ -12448,7 +12464,7 @@
       <c r="Q9" s="128"/>
       <c r="R9" s="128"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="66"/>
@@ -12476,11 +12492,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
@@ -12498,7 +12514,7 @@
       <c r="Q12" s="128"/>
       <c r="R12" s="128"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
@@ -12548,7 +12564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:18" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
         <v>39</v>
       </c>
@@ -12598,7 +12614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>90</v>
       </c>
@@ -12625,7 +12641,7 @@
       <c r="Q15" s="130"/>
       <c r="R15" s="130"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
         <f>L16</f>
         <v>FTE-COMCOA</v>
@@ -12670,7 +12686,7 @@
       <c r="Q16" s="128"/>
       <c r="R16" s="128"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-COMGAS</v>
@@ -12713,7 +12729,7 @@
       <c r="Q17" s="128"/>
       <c r="R17" s="128"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-COMOIL</v>
@@ -12759,7 +12775,7 @@
       <c r="Q18" s="128"/>
       <c r="R18" s="128"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="str">
         <f>'EB1'!$H$2</f>
         <v>KER</v>
@@ -12793,7 +12809,7 @@
       <c r="Q19" s="128"/>
       <c r="R19" s="128"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
         <f>'EB1'!$I$2</f>
         <v>LPG</v>
@@ -12827,7 +12843,7 @@
       <c r="Q20" s="128"/>
       <c r="R20" s="128"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
         <f>'EB1'!$J$2</f>
         <v>GSL</v>
@@ -12863,7 +12879,7 @@
       <c r="Q21" s="128"/>
       <c r="R21" s="128"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
         <f>'EB1'!$L$2</f>
         <v>HFO</v>
@@ -12877,7 +12893,7 @@
       <c r="H22" s="10"/>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
         <f>'EB1'!$M$2</f>
         <v>OPP</v>
@@ -12891,7 +12907,7 @@
       <c r="H23" s="10"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B24" t="str">
         <f>L19</f>
         <v>FTE-COMBIO</v>
@@ -12916,7 +12932,7 @@
       <c r="K24" s="23"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-COMSOL</v>
@@ -12941,7 +12957,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="str">
         <f>L21</f>
         <v>FTE-COMELC</v>
@@ -12968,7 +12984,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="66"/>
@@ -12977,20 +12993,20 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
       <c r="H28" s="10"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="11"/>
@@ -12998,7 +13014,7 @@
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="11"/>
@@ -13006,7 +13022,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="95"/>
@@ -13014,7 +13030,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -13022,7 +13038,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -13030,7 +13046,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="95"/>
@@ -13038,7 +13054,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="11"/>
@@ -13046,7 +13062,7 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="23"/>
       <c r="D37" s="23"/>
       <c r="E37" s="11"/>
@@ -13054,13 +13070,13 @@
       <c r="G37" s="66"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="39"/>
       <c r="C41" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="61"/>
       <c r="C42" s="1" t="s">
         <v>150</v>
@@ -13077,32 +13093,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:U35"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
     <col min="10" max="10" width="2" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="77.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" customWidth="1"/>
-    <col min="19" max="19" width="13.44140625" customWidth="1"/>
-    <col min="20" max="20" width="13.88671875" customWidth="1"/>
-    <col min="21" max="21" width="8.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.85546875" customWidth="1"/>
+    <col min="21" max="21" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -13125,7 +13141,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B6</f>
         <v>COM</v>
@@ -13164,7 +13180,7 @@
       <c r="T2" s="124"/>
       <c r="U2" s="124"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M3" s="125" t="s">
         <v>7</v>
       </c>
@@ -13193,7 +13209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -13227,7 +13243,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -13254,7 +13270,7 @@
       <c r="T5" s="124"/>
       <c r="U5" s="124"/>
     </row>
-    <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -13279,7 +13295,7 @@
       <c r="T6" s="124"/>
       <c r="U6" s="124"/>
     </row>
-    <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -13304,7 +13320,7 @@
       <c r="T7" s="124"/>
       <c r="U7" s="124"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M8" s="128" t="s">
         <v>106</v>
       </c>
@@ -13326,7 +13342,7 @@
       <c r="T8" s="128"/>
       <c r="U8" s="128"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
@@ -13346,7 +13362,7 @@
       <c r="T10" s="128"/>
       <c r="U10" s="128"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="17" t="s">
         <v>1</v>
       </c>
@@ -13403,7 +13419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
@@ -13460,7 +13476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>90</v>
       </c>
@@ -13490,7 +13506,7 @@
       <c r="T13" s="127"/>
       <c r="U13" s="127"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
         <f>O14</f>
         <v>CSCESOL</v>
@@ -13546,7 +13562,7 @@
       <c r="T14" s="128"/>
       <c r="U14" s="128"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="str">
         <f t="shared" ref="B15:B18" si="2">O15</f>
         <v>CSCEELC</v>
@@ -13603,7 +13619,7 @@
       <c r="T15" s="128"/>
       <c r="U15" s="128"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="105" t="str">
         <f t="shared" si="2"/>
         <v>CAPEELC</v>
@@ -13661,7 +13677,7 @@
       <c r="T16" s="131"/>
       <c r="U16" s="131"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f t="shared" si="2"/>
         <v>COTEOIL</v>
@@ -13718,7 +13734,7 @@
       <c r="T17" s="128"/>
       <c r="U17" s="128"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f t="shared" si="2"/>
         <v>COTEELC</v>
@@ -13775,61 +13791,61 @@
       <c r="T18" s="128"/>
       <c r="U18" s="128"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E19" s="6"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E20" s="6"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="P20" s="19"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E21" s="6"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="P21" s="19"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E22" s="6"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
       <c r="P22" s="19"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -13845,29 +13861,29 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:R38"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -13888,7 +13904,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B5</f>
         <v>RSD</v>
@@ -13924,7 +13940,7 @@
       <c r="Q2" s="124"/>
       <c r="R2" s="124"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J3" s="125" t="s">
         <v>7</v>
       </c>
@@ -13953,7 +13969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -13987,7 +14003,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="66"/>
@@ -14013,7 +14029,7 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="128"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="66"/>
@@ -14037,7 +14053,7 @@
       <c r="Q6" s="128"/>
       <c r="R6" s="128"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="66"/>
@@ -14061,7 +14077,7 @@
       <c r="Q7" s="128"/>
       <c r="R7" s="128"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="66"/>
@@ -14085,7 +14101,7 @@
       <c r="Q8" s="128"/>
       <c r="R8" s="128"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="66"/>
@@ -14109,7 +14125,7 @@
       <c r="Q9" s="128"/>
       <c r="R9" s="128"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="66"/>
@@ -14137,18 +14153,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="66"/>
       <c r="H11" s="10"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L12" s="23"/>
       <c r="M12" s="24"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
@@ -14166,7 +14182,7 @@
       <c r="Q13" s="128"/>
       <c r="R13" s="128"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B14" s="17" t="s">
         <v>1</v>
       </c>
@@ -14216,7 +14232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:18" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
         <v>39</v>
       </c>
@@ -14266,7 +14282,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>90</v>
       </c>
@@ -14293,7 +14309,7 @@
       <c r="Q16" s="130"/>
       <c r="R16" s="130"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-RSDCOA</v>
@@ -14338,7 +14354,7 @@
       <c r="Q17" s="128"/>
       <c r="R17" s="128"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-RSDGAS</v>
@@ -14381,7 +14397,7 @@
       <c r="Q18" s="128"/>
       <c r="R18" s="128"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
         <f>L19</f>
         <v>FTE-RSDOIL</v>
@@ -14426,7 +14442,7 @@
       <c r="Q19" s="128"/>
       <c r="R19" s="128"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
         <f>'EB1'!$H$2</f>
         <v>KER</v>
@@ -14460,7 +14476,7 @@
       <c r="Q20" s="128"/>
       <c r="R20" s="128"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
         <f>'EB1'!$I$2</f>
         <v>LPG</v>
@@ -14494,7 +14510,7 @@
       <c r="Q21" s="128"/>
       <c r="R21" s="128"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
         <f>'EB1'!$J$2</f>
         <v>GSL</v>
@@ -14530,7 +14546,7 @@
       <c r="Q22" s="128"/>
       <c r="R22" s="128"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
         <f>'EB1'!$L$2</f>
         <v>HFO</v>
@@ -14544,7 +14560,7 @@
       <c r="H23" s="10"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C24" t="str">
         <f>'EB1'!$M$2</f>
         <v>OPP</v>
@@ -14558,7 +14574,7 @@
       <c r="H24" s="10"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-RSDBIO</v>
@@ -14583,7 +14599,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" t="str">
         <f>L21</f>
         <v>FTE-RSDSOL</v>
@@ -14608,7 +14624,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" t="str">
         <f>L22</f>
         <v>FTE-RSDELC</v>
@@ -14635,7 +14651,7 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
@@ -14644,20 +14660,20 @@
       <c r="K28" s="23"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
       <c r="M29" s="19"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="39"/>
       <c r="C31" s="1" t="s">
         <v>149</v>
@@ -14668,7 +14684,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="61"/>
       <c r="C32" s="1" t="s">
         <v>150</v>
@@ -14679,7 +14695,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -14687,7 +14703,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -14695,7 +14711,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="95"/>
@@ -14703,7 +14719,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="95"/>
@@ -14711,7 +14727,7 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="23"/>
       <c r="D37" s="23"/>
       <c r="E37" s="11"/>
@@ -14719,7 +14735,7 @@
       <c r="G37" s="66"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="23"/>
       <c r="D38" s="23"/>
       <c r="E38" s="11"/>
@@ -14738,32 +14754,32 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:U35"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
     <col min="10" max="10" width="2" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="77.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" customWidth="1"/>
-    <col min="19" max="19" width="13.44140625" customWidth="1"/>
-    <col min="20" max="20" width="13.88671875" customWidth="1"/>
-    <col min="21" max="21" width="8.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.85546875" customWidth="1"/>
+    <col min="21" max="21" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:21" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -14786,7 +14802,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B5</f>
         <v>RSD</v>
@@ -14825,7 +14841,7 @@
       <c r="T2" s="124"/>
       <c r="U2" s="124"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M3" s="125" t="s">
         <v>7</v>
       </c>
@@ -14854,7 +14870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -14888,7 +14904,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -14915,7 +14931,7 @@
       <c r="T5" s="124"/>
       <c r="U5" s="124"/>
     </row>
-    <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -14940,7 +14956,7 @@
       <c r="T6" s="124"/>
       <c r="U6" s="124"/>
     </row>
-    <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -14965,7 +14981,7 @@
       <c r="T7" s="124"/>
       <c r="U7" s="124"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M8" s="128" t="s">
         <v>106</v>
       </c>
@@ -14987,7 +15003,7 @@
       <c r="T8" s="128"/>
       <c r="U8" s="128"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
@@ -15007,7 +15023,7 @@
       <c r="T10" s="128"/>
       <c r="U10" s="128"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="17" t="s">
         <v>1</v>
       </c>
@@ -15064,7 +15080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
@@ -15121,7 +15137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>90</v>
       </c>
@@ -15151,7 +15167,7 @@
       <c r="T13" s="127"/>
       <c r="U13" s="127"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="str">
         <f t="shared" ref="B14:B18" si="0">O14</f>
         <v>RSCEELC</v>
@@ -15207,7 +15223,7 @@
       <c r="T14" s="128"/>
       <c r="U14" s="128"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="105" t="str">
         <f t="shared" si="0"/>
         <v>RAPEELC</v>
@@ -15264,7 +15280,7 @@
       <c r="T15" s="131"/>
       <c r="U15" s="131"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>ROTEOIL</v>
@@ -15321,7 +15337,7 @@
       <c r="T16" s="128"/>
       <c r="U16" s="128"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>ROTEBIO</v>
@@ -15378,7 +15394,7 @@
       <c r="T17" s="128"/>
       <c r="U17" s="128"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>ROTEELC</v>
@@ -15435,67 +15451,67 @@
       <c r="T18" s="128"/>
       <c r="U18" s="128"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E19" s="6"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E20" s="6"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="P20" s="19"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E21" s="6"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="P21" s="19"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E22" s="6"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
       <c r="P22" s="19"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
       <c r="G25" s="1"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -15511,20 +15527,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:K32"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -15538,7 +15554,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>83</v>
       </c>
@@ -15549,7 +15565,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -15560,7 +15576,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>80</v>
       </c>
@@ -15586,7 +15602,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B7" s="15" t="s">
         <v>81</v>
       </c>
@@ -15608,7 +15624,7 @@
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
     </row>
-    <row r="8" spans="2:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>90</v>
       </c>
@@ -15625,7 +15641,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="25" t="s">
         <v>35</v>
       </c>
@@ -15654,7 +15670,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -15683,7 +15699,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>35</v>
       </c>
@@ -15712,7 +15728,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
@@ -15741,7 +15757,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -15770,7 +15786,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>35</v>
       </c>
@@ -15799,7 +15815,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
         <v>35</v>
       </c>
@@ -15829,7 +15845,7 @@
       </c>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
         <v>35</v>
       </c>
@@ -15858,7 +15874,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
         <v>35</v>
       </c>
@@ -15887,7 +15903,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G18" s="1" t="s">
         <v>123</v>
       </c>
@@ -15902,7 +15918,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G19" s="1" t="s">
         <v>123</v>
       </c>
@@ -15917,7 +15933,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G20" s="26" t="s">
         <v>123</v>
       </c>
@@ -15932,7 +15948,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G21" s="1" t="s">
         <v>123</v>
       </c>
@@ -15947,7 +15963,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G22" s="1" t="s">
         <v>123</v>
       </c>
@@ -15962,7 +15978,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G23" s="1" t="s">
         <v>123</v>
       </c>
@@ -15977,7 +15993,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G24" s="26" t="s">
         <v>123</v>
       </c>
@@ -15992,7 +16008,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G25" s="1" t="s">
         <v>123</v>
       </c>
@@ -16007,7 +16023,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G26" s="1" t="s">
         <v>123</v>
       </c>
@@ -16022,7 +16038,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G27" s="1" t="s">
         <v>123</v>
       </c>
@@ -16037,7 +16053,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G28" s="26" t="s">
         <v>123</v>
       </c>
@@ -16052,7 +16068,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G29" s="1" t="s">
         <v>123</v>
       </c>
@@ -16067,7 +16083,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
@@ -16086,7 +16102,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
@@ -16105,7 +16121,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G32" s="26" t="s">
         <v>123</v>
       </c>
